--- a/data/input.xlsx
+++ b/data/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\congn\Documents\tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB81CB04-B00F-495A-A09B-76820F3FBFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17833D2-58F2-4007-8E11-4D8C86307926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>id</t>
   </si>
@@ -29,13 +29,22 @@
   </si>
   <si>
     <t>serial</t>
+  </si>
+  <si>
+    <t>ngay_cap</t>
+  </si>
+  <si>
+    <t>noi_cap</t>
+  </si>
+  <si>
+    <t>GUWAHATI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -46,6 +55,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -71,9 +86,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -376,13 +392,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="11.125" customWidth="1"/>
+    <col min="4" max="4" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -392,8 +409,14 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -402,6 +425,12 @@
       </c>
       <c r="C2" s="1">
         <v>1163972931</v>
+      </c>
+      <c r="D2" s="2">
+        <v>43608</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/input.xlsx
+++ b/data/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\congn\Documents\tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17833D2-58F2-4007-8E11-4D8C86307926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D7D623-EDA9-463C-93EE-D6312C0F6D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>id</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>GUWAHATI</t>
+  </si>
+  <si>
+    <t>RANCHI</t>
   </si>
 </sst>
 </file>
@@ -392,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="11.125" customWidth="1"/>
@@ -427,9 +430,26 @@
         <v>1163972931</v>
       </c>
       <c r="D2" s="2">
+        <v>45814</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>814560106</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1163972931</v>
+      </c>
+      <c r="D3" s="2">
         <v>43608</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/data/input.xlsx
+++ b/data/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\congn\Documents\tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D7D623-EDA9-463C-93EE-D6312C0F6D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C3C589-F966-4965-AA61-25B0FE09CC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>id</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>noi_cap</t>
-  </si>
-  <si>
-    <t>GUWAHATI</t>
   </si>
   <si>
     <t>RANCHI</t>
@@ -433,25 +430,13 @@
         <v>45814</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <v>814560106</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1163972931</v>
-      </c>
-      <c r="D3" s="2">
-        <v>43608</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input.xlsx
+++ b/data/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\congn\Documents\tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C3C589-F966-4965-AA61-25B0FE09CC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C029F58F-1478-4FD0-8F51-DD54ACB2A248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>id</t>
   </si>
@@ -38,6 +38,12 @@
   </si>
   <si>
     <t>RANCHI</t>
+  </si>
+  <si>
+    <t>MINISTRY OF HOME AFFAIRS</t>
+  </si>
+  <si>
+    <t>МВД 02101</t>
   </si>
 </sst>
 </file>
@@ -86,10 +92,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -392,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="11.125" customWidth="1"/>
@@ -434,9 +441,38 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>84832037122</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2228055088</v>
+      </c>
+      <c r="D3" s="3">
+        <v>45325</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>84832041950</v>
+      </c>
+      <c r="C4">
+        <v>2228055301</v>
+      </c>
+      <c r="D4" s="3">
+        <v>45278</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input.xlsx
+++ b/data/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\congn\Documents\tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C029F58F-1478-4FD0-8F51-DD54ACB2A248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C812029E-5DD3-4858-864B-5EDA79A60A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>id</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>RANCHI</t>
-  </si>
-  <si>
-    <t>MINISTRY OF HOME AFFAIRS</t>
   </si>
   <si>
     <t>МВД 02101</t>
@@ -445,34 +442,20 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>84832037122</v>
+        <v>84812573457</v>
       </c>
       <c r="C3" s="1">
-        <v>2228055088</v>
+        <v>2228055418</v>
       </c>
       <c r="D3" s="3">
-        <v>45325</v>
+        <v>45278</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>84832041950</v>
-      </c>
-      <c r="C4">
-        <v>2228055301</v>
-      </c>
-      <c r="D4" s="3">
-        <v>45278</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
+      <c r="D4" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input.xlsx
+++ b/data/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\congn\Documents\tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C812029E-5DD3-4858-864B-5EDA79A60A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCFF241F-5196-4D7C-9399-23C57A764378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>id</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>МВД 02101</t>
+  </si>
+  <si>
+    <t>MINISTRY OF HOME AFFAIRS</t>
   </si>
 </sst>
 </file>
@@ -455,7 +458,21 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D4" s="3"/>
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>84832037122</v>
+      </c>
+      <c r="C4">
+        <v>2228055088</v>
+      </c>
+      <c r="D4" s="3">
+        <v>45325</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
